--- a/jpcore-r4/main/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-location.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -301,10 +301,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -340,7 +340,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
+    <t>リソースコンテンツの言語</t>
   </si>
   <si>
     <t>リソースが書かれている基本言語。</t>
@@ -352,7 +352,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -398,7 +398,7 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
+    <t>含まれている、インラインのリソース</t>
   </si>
   <si>
     <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
@@ -443,7 +443,7 @@
     <t>Location.modifierExtension</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
+    <t>無視できない拡張機能</t>
   </si>
   <si>
     <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
@@ -489,7 +489,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>「場所がまだ使用されているかどうかを示します。」</t>
+    <t>場所がまだ使用されているかどうかを示します。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/location-status|4.0.1</t>
@@ -619,7 +619,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>「場所で行われる機能のタイプを示します。」</t>
+    <t>場所で行われる機能のタイプを示します。</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
@@ -868,7 +868,7 @@
     <t>FHIR文字列のサイズは1MBを超えてはならないことに注意すること。</t>
   </si>
   <si>
-    <t>曜日 (Youbi)</t>
+    <t>曜日</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/days-of-week|4.0.1</t>

--- a/jpcore-r4/main/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-location.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-location.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -437,7 +437,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Location.modifierExtension</t>

--- a/jpcore-r4/main/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-location.xlsx
@@ -1233,17 +1233,17 @@
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="42.98046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.98046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="36.84765625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="36.84765625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="65.7578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="56.37890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1252,24 +1252,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="43.953125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.31640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="37.6796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.84765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="68.15625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="58.43359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-location.xlsx
@@ -355,7 +355,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -687,7 +687,7 @@
     <t>場所の実体形態。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -916,7 +916,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/main/StructureDefinition-jp-location.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-location.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
